--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261014.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261014.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>267,341,598</t>
+          <t>8,591,740</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>8,591,740</t>
+          <t>267,341,598</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>30,082,227</t>
+          <t>2,031,625</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,031,625</t>
+          <t>30,082,227</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>216,577,896</t>
+          <t>261,256,234</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>261,256,234</t>
+          <t>216,577,896</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>18,410,845</t>
+          <t>8,115,742</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,115,742</t>
+          <t>18,410,845</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>10,753,195</t>
+          <t>26,666,996</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>26,666,996</t>
+          <t>10,753,195</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
